--- a/DateBase/orders/Nha Thu_2026-8-26.xlsx
+++ b/DateBase/orders/Nha Thu_2026-8-26.xlsx
@@ -523,6 +523,9 @@
       <c r="A11" t="str">
         <v>4</v>
       </c>
+      <c r="C11" t="str">
+        <v>422_粉黛_pink muhly grass_undefined_1bunch</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>

--- a/DateBase/orders/Nha Thu_2026-8-26.xlsx
+++ b/DateBase/orders/Nha Thu_2026-8-26.xlsx
@@ -526,6 +526,9 @@
       <c r="C11" t="str">
         <v>422_粉黛_pink muhly grass_undefined_1bunch</v>
       </c>
+      <c r="F11" t="str">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -584,7 +587,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0121317911126750</v>
+        <v>0121317911126751</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-8-26.xlsx
+++ b/DateBase/orders/Nha Thu_2026-8-26.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -527,12 +527,36 @@
         <v>422_粉黛_pink muhly grass_undefined_1bunch</v>
       </c>
       <c r="F11" t="str">
-        <v>1</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>389_金合欢_mimosa_undefined_1bunch</v>
+      </c>
+      <c r="F12" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>780_贝壳草_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F13" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>585_洋牡丹红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F14" t="str">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L14"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -587,7 +611,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0121317911126751</v>
+        <v>0121317911126751515520</v>
       </c>
     </row>
   </sheetData>
